--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N6_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>53.78672723343436</v>
       </c>
       <c r="E2" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F2" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>51.47075700456132</v>
       </c>
       <c r="E3" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F3" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>52.35080740312469</v>
       </c>
       <c r="E4" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F4" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>44.5642735497215</v>
       </c>
       <c r="E5" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F5" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>41.37957218367423</v>
       </c>
       <c r="E6" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F6" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>35.97303218688519</v>
       </c>
       <c r="E7" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F7" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>24.55181723739119</v>
       </c>
       <c r="E8" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F8" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>50.70550768333754</v>
       </c>
       <c r="E9" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F9" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>24.39955303258781</v>
       </c>
       <c r="E10" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F10" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         <v>8.242827384691173</v>
       </c>
       <c r="E11" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F11" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>9.270817130525822</v>
       </c>
       <c r="E12" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F12" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         <v>43.27306322863876</v>
       </c>
       <c r="E13" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F13" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>41.83422238216112</v>
       </c>
       <c r="E14" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F14" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>41.7312005268307</v>
+        <v>22.69515923117927</v>
       </c>
       <c r="D15" t="n">
-        <v>40.35771111459697</v>
+        <v>18.40066465718183</v>
       </c>
       <c r="E15" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F15" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>34.74816278378245</v>
+        <v>41.7312005268307</v>
       </c>
       <c r="D16" t="n">
-        <v>34.16301161944806</v>
+        <v>40.35771111459697</v>
       </c>
       <c r="E16" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F16" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>43.47432053044781</v>
+        <v>34.74816278378245</v>
       </c>
       <c r="D17" t="n">
-        <v>42.23228812600606</v>
+        <v>34.16301161944806</v>
       </c>
       <c r="E17" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F17" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>44.5699012205149</v>
+        <v>43.47432053044781</v>
       </c>
       <c r="D18" t="n">
-        <v>45.03595233469795</v>
+        <v>42.23228812600606</v>
       </c>
       <c r="E18" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F18" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>44.19205786981462</v>
+        <v>44.5699012205149</v>
       </c>
       <c r="D19" t="n">
-        <v>43.80847064938931</v>
+        <v>45.03595233469795</v>
       </c>
       <c r="E19" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F19" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>42.50797898996107</v>
+        <v>44.19205786981462</v>
       </c>
       <c r="D20" t="n">
-        <v>41.61613496792553</v>
+        <v>43.80847064938931</v>
       </c>
       <c r="E20" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F20" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>54.06009932788572</v>
+        <v>42.50797898996107</v>
       </c>
       <c r="D21" t="n">
-        <v>53.01567323746104</v>
+        <v>41.61613496792553</v>
       </c>
       <c r="E21" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F21" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>42.43298933597439</v>
+        <v>54.06009932788572</v>
       </c>
       <c r="D22" t="n">
-        <v>35.00795338205306</v>
+        <v>53.01567323746104</v>
       </c>
       <c r="E22" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F22" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>62.33796548812357</v>
+        <v>42.43298933597439</v>
       </c>
       <c r="D23" t="n">
-        <v>61.11550856021275</v>
+        <v>35.00795338205306</v>
       </c>
       <c r="E23" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F23" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>53.09409858438984</v>
+        <v>62.33796548812357</v>
       </c>
       <c r="D24" t="n">
-        <v>52.39891052961421</v>
+        <v>61.11550856021275</v>
       </c>
       <c r="E24" t="n">
-        <v>13.28380033909082</v>
+        <v>13.52411130302468</v>
       </c>
       <c r="F24" t="n">
-        <v>13.0881903394932</v>
+        <v>13.5671331072972</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,23 +1216,55 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
+        <v>53.09409858438984</v>
+      </c>
+      <c r="D25" t="n">
+        <v>52.39891052961421</v>
+      </c>
+      <c r="E25" t="n">
+        <v>13.52411130302468</v>
+      </c>
+      <c r="F25" t="n">
+        <v>13.5671331072972</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>T6758</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>W0045F0002T0006Z000C1N6.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" t="n">
         <v>53.68256248697517</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D26" t="n">
         <v>53.53352630860114</v>
       </c>
-      <c r="E25" t="n">
-        <v>13.28380033909082</v>
-      </c>
-      <c r="F25" t="n">
-        <v>13.0881903394932</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>T6758</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="E26" t="n">
+        <v>13.52411130302468</v>
+      </c>
+      <c r="F26" t="n">
+        <v>13.5671331072972</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>T6758</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.13712774714261</v>
+        <v>8.634783258910675</v>
       </c>
       <c r="D2" t="n">
-        <v>53.78672723343436</v>
+        <v>8.740343175433082</v>
       </c>
       <c r="E2" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F2" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>51.45328129915539</v>
+        <v>8.361158211112752</v>
       </c>
       <c r="D3" t="n">
-        <v>51.47075700456132</v>
+        <v>8.363998013241215</v>
       </c>
       <c r="E3" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F3" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.21746467887129</v>
+        <v>8.322838010316586</v>
       </c>
       <c r="D4" t="n">
-        <v>52.35080740312469</v>
+        <v>8.507006203007762</v>
       </c>
       <c r="E4" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F4" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.57715449244207</v>
+        <v>7.081287605021837</v>
       </c>
       <c r="D5" t="n">
-        <v>44.5642735497215</v>
+        <v>7.241694451829744</v>
       </c>
       <c r="E5" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F5" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.90936129147109</v>
+        <v>6.647771209864052</v>
       </c>
       <c r="D6" t="n">
-        <v>41.37957218367423</v>
+        <v>6.724180479847062</v>
       </c>
       <c r="E6" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F6" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.10856806110518</v>
+        <v>5.867642309929592</v>
       </c>
       <c r="D7" t="n">
-        <v>35.97303218688519</v>
+        <v>5.845617730368843</v>
       </c>
       <c r="E7" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F7" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.28439008659148</v>
+        <v>3.946213389071115</v>
       </c>
       <c r="D8" t="n">
-        <v>24.55181723739119</v>
+        <v>3.989670301076069</v>
       </c>
       <c r="E8" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F8" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.67438652829051</v>
+        <v>8.397087810847209</v>
       </c>
       <c r="D9" t="n">
-        <v>50.70550768333754</v>
+        <v>8.239644998542349</v>
       </c>
       <c r="E9" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F9" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>25.45278498721631</v>
+        <v>4.136077560422651</v>
       </c>
       <c r="D10" t="n">
-        <v>24.39955303258781</v>
+        <v>3.96492736779552</v>
       </c>
       <c r="E10" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F10" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>7.68049991601159</v>
+        <v>1.248081236351883</v>
       </c>
       <c r="D11" t="n">
-        <v>8.242827384691173</v>
+        <v>1.339459450012316</v>
       </c>
       <c r="E11" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F11" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>7.924360282607082</v>
+        <v>1.287708545923651</v>
       </c>
       <c r="D12" t="n">
-        <v>9.270817130525822</v>
+        <v>1.506507783710446</v>
       </c>
       <c r="E12" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F12" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.24632400757556</v>
+        <v>6.865027651231029</v>
       </c>
       <c r="D13" t="n">
-        <v>43.27306322863876</v>
+        <v>7.031872774653799</v>
       </c>
       <c r="E13" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F13" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>42.19693333932468</v>
+        <v>6.857001667640261</v>
       </c>
       <c r="D14" t="n">
-        <v>41.83422238216112</v>
+        <v>6.798061137101183</v>
       </c>
       <c r="E14" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F14" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>22.69515923117927</v>
+        <v>3.687963375066632</v>
       </c>
       <c r="D15" t="n">
-        <v>18.40066465718183</v>
+        <v>2.990108006792047</v>
       </c>
       <c r="E15" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F15" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>41.7312005268307</v>
+        <v>6.781320085609988</v>
       </c>
       <c r="D16" t="n">
-        <v>40.35771111459697</v>
+        <v>6.558128056122007</v>
       </c>
       <c r="E16" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F16" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>34.74816278378245</v>
+        <v>5.646576452364648</v>
       </c>
       <c r="D17" t="n">
-        <v>34.16301161944806</v>
+        <v>5.55148938816031</v>
       </c>
       <c r="E17" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F17" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>43.47432053044781</v>
+        <v>7.064577086197769</v>
       </c>
       <c r="D18" t="n">
-        <v>42.23228812600606</v>
+        <v>6.862746820475985</v>
       </c>
       <c r="E18" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F18" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>44.5699012205149</v>
+        <v>7.242608948333672</v>
       </c>
       <c r="D19" t="n">
-        <v>45.03595233469795</v>
+        <v>7.318342254388416</v>
       </c>
       <c r="E19" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F19" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>44.19205786981462</v>
+        <v>7.181209403844876</v>
       </c>
       <c r="D20" t="n">
-        <v>43.80847064938931</v>
+        <v>7.118876480525763</v>
       </c>
       <c r="E20" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F20" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>42.50797898996107</v>
+        <v>6.907546585868674</v>
       </c>
       <c r="D21" t="n">
-        <v>41.61613496792553</v>
+        <v>6.7626219322879</v>
       </c>
       <c r="E21" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F21" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>54.06009932788572</v>
+        <v>8.784766140781429</v>
       </c>
       <c r="D22" t="n">
-        <v>53.01567323746104</v>
+        <v>8.615046901087419</v>
       </c>
       <c r="E22" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F22" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>42.43298933597439</v>
+        <v>6.895360767095839</v>
       </c>
       <c r="D23" t="n">
-        <v>35.00795338205306</v>
+        <v>5.688792424583623</v>
       </c>
       <c r="E23" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F23" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>62.33796548812357</v>
+        <v>10.12991939182008</v>
       </c>
       <c r="D24" t="n">
-        <v>61.11550856021275</v>
+        <v>9.931270141034572</v>
       </c>
       <c r="E24" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F24" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>53.09409858438984</v>
+        <v>8.627791019963349</v>
       </c>
       <c r="D25" t="n">
-        <v>52.39891052961421</v>
+        <v>8.514822961062309</v>
       </c>
       <c r="E25" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F25" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>53.68256248697517</v>
+        <v>8.723416404133467</v>
       </c>
       <c r="D26" t="n">
-        <v>53.53352630860114</v>
+        <v>8.699198025147686</v>
       </c>
       <c r="E26" t="n">
-        <v>13.52411130302468</v>
+        <v>2.19766808674151</v>
       </c>
       <c r="F26" t="n">
-        <v>13.5671331072972</v>
+        <v>2.204659129935794</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
